--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487914_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487914_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1428</v>
+        <v>6.7642</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8728</v>
+        <v>5.0715</v>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.6927</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0818</v>
+        <v>4.9892</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0681</v>
+        <v>-2.9407</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9862</v>
+        <v>7.9299</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1429</v>
+        <v>5.4058</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.3372</v>
+        <v>-2.8751</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4802</v>
+        <v>8.280900000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2248</v>
+        <v>-0.4166</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2692</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4939</v>
+        <v>-0.351</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3703</v>
+        <v>0.9644</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3324</v>
+        <v>0.4763</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0379</v>
+        <v>0.4881</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3975</v>
+        <v>-0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6946</v>
+        <v>5.0858</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1194</v>
+        <v>3.6103</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5753</v>
+        <v>1.4755</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9892</v>
+        <v>-0.0818</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.9407</v>
+        <v>-1.0681</v>
       </c>
       <c r="I3" t="n">
-        <v>7.9299</v>
+        <v>0.9862</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4058</v>
+        <v>0.1429</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.8751</v>
+        <v>-1.3372</v>
       </c>
       <c r="L3" t="n">
-        <v>8.280900000000001</v>
+        <v>1.4802</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4166</v>
+        <v>-0.2248</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.2692</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.351</v>
+        <v>-0.4939</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1052</v>
+        <v>2.3132</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4758</v>
+        <v>2.0698</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3706</v>
+        <v>0.2434</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="W3" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3038</v>
+        <v>2.9695</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2292</v>
+        <v>1.8362</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0746</v>
+        <v>1.1333</v>
       </c>
       <c r="G4" t="n">
         <v>3.5448</v>
@@ -766,13 +766,13 @@
         <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3128</v>
+        <v>0.9784</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2298</v>
+        <v>0.8368</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0829</v>
+        <v>0.1416</v>
       </c>
       <c r="V4" t="n">
         <v>-1.7619</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7391</v>
+        <v>2.2817</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6533</v>
+        <v>3.2839</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9142</v>
+        <v>-1.0023</v>
       </c>
       <c r="G5" t="n">
         <v>2.284</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2388</v>
+        <v>1.3038</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8762</v>
+        <v>0.7544</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6375</v>
+        <v>0.5494</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5142</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0873</v>
+        <v>-0.0328</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0672</v>
+        <v>-3.2643</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9799</v>
+        <v>3.2314</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6434</v>
+        <v>-2.4302</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8231</v>
+        <v>-1.386</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1797</v>
+        <v>-1.0442</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3616</v>
+        <v>-3.3565</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1453</v>
+        <v>-2.2715</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7838000000000001</v>
+        <v>-1.085</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2818</v>
+        <v>0.9264</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6778</v>
+        <v>0.8855</v>
       </c>
       <c r="O6" t="n">
-        <v>0.396</v>
+        <v>0.0408</v>
       </c>
       <c r="P6" t="n">
         <v>-0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3977</v>
+        <v>1.5547</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5932</v>
+        <v>1.0059</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8045</v>
+        <v>0.5488</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4589</v>
+        <v>1.0508</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1238</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3351</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0129</v>
+        <v>-1.3808</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3948</v>
+        <v>-0.1953</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4076</v>
+        <v>-1.1855</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4302</v>
+        <v>-0.6434</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.386</v>
+        <v>-1.8231</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0442</v>
+        <v>1.1797</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.3565</v>
+        <v>-0.3616</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2715</v>
+        <v>-1.1453</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.085</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9264</v>
+        <v>-0.2818</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8855</v>
+        <v>-0.6778</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0408</v>
+        <v>0.396</v>
       </c>
       <c r="P7" t="n">
         <v>-0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6004</v>
+        <v>1.9296</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8754</v>
+        <v>1.3307</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7249</v>
+        <v>0.599</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0508</v>
+        <v>-2.4589</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>-0.1238</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1168</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8342</v>
+        <v>-1.7017</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9985</v>
+        <v>-3.5986</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1643</v>
+        <v>1.897</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7728</v>
+        <v>-1.9651</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8528</v>
+        <v>0.7037</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08</v>
+        <v>-2.6689</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6191</v>
+        <v>-2.4957</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8575</v>
+        <v>-0.431</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2384</v>
+        <v>-2.0647</v>
       </c>
       <c r="M8" t="n">
-        <v>1.392</v>
+        <v>0.5306</v>
       </c>
       <c r="N8" t="n">
-        <v>1.7104</v>
+        <v>1.1347</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3184</v>
+        <v>-0.6041</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7366</v>
+        <v>0.2345</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2824</v>
+        <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4541</v>
+        <v>0.2969</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0543</v>
+        <v>0.237</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5142</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5208</v>
+        <v>-1.708</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2416</v>
+        <v>-2.7842</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7208</v>
+        <v>1.0762</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9651</v>
+        <v>0.7728</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7037</v>
+        <v>0.8528</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6689</v>
+        <v>-0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4957</v>
+        <v>-0.6191</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.431</v>
+        <v>-0.8575</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0647</v>
+        <v>0.2384</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5306</v>
+        <v>1.392</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1347</v>
+        <v>1.7104</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6041</v>
+        <v>-0.3184</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R9" t="n">
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5845</v>
+        <v>0.8628</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7053</v>
+        <v>0.4968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1207</v>
+        <v>0.3661</v>
       </c>
       <c r="V9" t="n">
-        <v>0.237</v>
+        <v>-1.0543</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X9" t="n">
-        <v>0.237</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>11.6255</v>
+        <v>12.2779</v>
       </c>
       <c r="E10" t="n">
-        <v>3.307</v>
+        <v>3.9595</v>
       </c>
       <c r="F10" t="n">
-        <v>8.3185</v>
+        <v>8.318300000000001</v>
       </c>
       <c r="G10" t="n">
         <v>6.4703</v>
@@ -1234,13 +1234,13 @@
         <v>10.406</v>
       </c>
       <c r="S10" t="n">
-        <v>9.4893</v>
+        <v>10.1414</v>
       </c>
       <c r="T10" t="n">
-        <v>6.2559</v>
+        <v>6.9083</v>
       </c>
       <c r="U10" t="n">
-        <v>3.233099999999999</v>
+        <v>3.2333</v>
       </c>
       <c r="V10" t="n">
         <v>-4.334</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1112</v>
+        <v>1.4033</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4348</v>
+        <v>-0.2319</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3236</v>
+        <v>1.6352</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6142</v>
+        <v>2.1954</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4649</v>
+        <v>0.8124</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8507</v>
+        <v>1.383</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7492</v>
+        <v>0.5586</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7181</v>
+        <v>0.1063</v>
       </c>
       <c r="L11" t="n">
-        <v>1.0311</v>
+        <v>0.4523</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.135</v>
+        <v>1.6368</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7468</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8818</v>
+        <v>0.9307</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8731</v>
+        <v>1.8731</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4325</v>
+        <v>-1.1438</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5774</v>
+        <v>-0.4367</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1449</v>
+        <v>-0.7071</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9376</v>
+        <v>-1.5213</v>
       </c>
       <c r="W11" t="n">
-        <v>0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9175</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5533</v>
+        <v>1.427</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4708</v>
+        <v>-0.5706</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1954</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8124</v>
+        <v>1.5377</v>
       </c>
       <c r="I12" t="n">
-        <v>1.383</v>
+        <v>-2.277</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5586</v>
+        <v>0.2896</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1063</v>
+        <v>0.648</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4523</v>
+        <v>-0.3584</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6368</v>
+        <v>-1.0289</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9307</v>
+        <v>-1.9186</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6297</v>
+        <v>-1.9662</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7581</v>
+        <v>-0.6138</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-1.3524</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5213</v>
+        <v>2.1051</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3538</v>
+        <v>1.7513</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5891</v>
+        <v>0.4717</v>
       </c>
       <c r="E13" t="n">
         <v>-0.0261</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6152</v>
+        <v>0.4977</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0098</v>
@@ -1468,13 +1468,13 @@
         <v>0.4162</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1827</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T13" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2479</v>
+        <v>0.1305</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3391</v>
+        <v>0.3269</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1203</v>
+        <v>0.0418</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4594</v>
+        <v>0.2851</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6434</v>
+        <v>1.6142</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5373</v>
+        <v>2.4649</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1061</v>
+        <v>-0.8507</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.676</v>
+        <v>2.7492</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.676</v>
+        <v>1.7181</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.0311</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0326</v>
+        <v>-1.135</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1387</v>
+        <v>0.7468</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1061</v>
+        <v>-1.8818</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6244</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3582</v>
+        <v>-0.3518</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4443</v>
+        <v>0.1844</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8025</v>
+        <v>-0.5362</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.9376</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. KALINICENKO</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0331</v>
+        <v>0.1821</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1765</v>
+        <v>-1.0132</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1434</v>
+        <v>1.1952</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2788</v>
+        <v>-0.6434</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0298</v>
+        <v>-0.5373</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.249</v>
+        <v>-0.1061</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0192</v>
+        <v>-0.676</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0192</v>
+        <v>-0.676</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.298</v>
+        <v>0.0326</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.049</v>
+        <v>0.1387</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.249</v>
+        <v>-0.1061</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4619</v>
+        <v>0.2011</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1957</v>
+        <v>-0.3372</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2662</v>
+        <v>0.5383</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>E. KALINICENKO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1413</v>
+        <v>-0.0038</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8912</v>
+        <v>-0.1765</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0325</v>
+        <v>0.1728</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.2788</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5377</v>
+        <v>-0.0298</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.277</v>
+        <v>-0.249</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2896</v>
+        <v>0.0192</v>
       </c>
       <c r="K16" t="n">
-        <v>0.648</v>
+        <v>0.0192</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3584</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0289</v>
+        <v>-0.298</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8897</v>
+        <v>-0.049</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9186</v>
+        <v>-0.249</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.9639</v>
+        <v>-0.4325</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1496</v>
+        <v>-0.1957</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.8143</v>
+        <v>-0.2368</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1051</v>
+        <v>0.7076</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3538</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5423</v>
+        <v>-0.4454</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8789</v>
+        <v>-0.6646</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3366</v>
+        <v>0.2192</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9521</v>
@@ -1780,13 +1780,13 @@
         <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3256</v>
+        <v>0.4224</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.64</v>
+        <v>-0.4257</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9656</v>
+        <v>0.8482</v>
       </c>
       <c r="V17" t="n">
         <v>0.4599</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3126</v>
+        <v>-1.5411</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9626</v>
+        <v>-1.0698</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.35</v>
+        <v>-0.4714</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0432</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4338</v>
+        <v>-0.6623</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.2038</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3372</v>
+        <v>-0.4586</v>
       </c>
       <c r="V18" t="n">
         <v>0.1238</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2633</v>
+        <v>-1.8942</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.407</v>
+        <v>0.2359</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8563</v>
+        <v>-2.1301</v>
       </c>
       <c r="G19" t="n">
         <v>0.3169</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.1015</v>
+        <v>-1.7325</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1372</v>
+        <v>-0.4943</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.9643</v>
+        <v>-1.2382</v>
       </c>
       <c r="V19" t="n">
         <v>0.3538</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3331</v>
+        <v>-2.676</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6735</v>
+        <v>-3.5663</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3404</v>
+        <v>0.8904</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5731000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1783</v>
+        <v>-0.5211</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4972</v>
+        <v>-0.39</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6811</v>
+        <v>-0.1311</v>
       </c>
       <c r="V20" t="n">
         <v>0.7076</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9566</v>
+        <v>-6.1621</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6162</v>
+        <v>-3.0449</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3404</v>
+        <v>-3.1173</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3569</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.019</v>
+        <v>-1.2246</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1734</v>
+        <v>-0.2552</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1925</v>
+        <v>-0.9694</v>
       </c>
       <c r="V21" t="n">
         <v>0.4599</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.6254</v>
+        <v>-9.482199999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.0884</v>
+        <v>-8.0886</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.536999999999999</v>
+        <v>-1.3938</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.470200000000002</v>
+        <v>-6.470200000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2448999999999995</v>
+        <v>-0.2448999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.225099999999999</v>
+        <v>-6.225100000000001</v>
       </c>
       <c r="J22" t="n">
         <v>-1.8967</v>
@@ -2170,13 +2170,13 @@
         <v>10.406</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.489100000000001</v>
+        <v>-7.346099999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.2331</v>
+        <v>-3.2332</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.255999999999999</v>
+        <v>-4.1128</v>
       </c>
       <c r="V22" t="n">
         <v>4.334000000000001</v>
